--- a/StructureDefinition-Provrelaterad-aktivitet-Aktivitet.xlsx
+++ b/StructureDefinition-Provrelaterad-aktivitet-Aktivitet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Provrelaterad-aktivitet-Aktivitet.xlsx
+++ b/StructureDefinition-Provrelaterad-aktivitet-Aktivitet.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Provrelaterad aktivitet: Aktivitet).</t>
+    <t>Klassen Provrelaterad aktivitet håller information om aktiviteter relaterade till hantering av prov.
+Inkluderar även t.ex. aktiviteter i samband med transport, frysning, förvaring, bearbetning och delning i sekundärprov.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -260,6 +261,10 @@
     <t>Source attribute: kod</t>
   </si>
   <si>
+    <t>Kod för provrelaterad aktivitet.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
+  </si>
+  <si>
     <t>Provrelaterad-aktivitet-Aktivitet.tid</t>
   </si>
   <si>
@@ -270,10 +275,17 @@
     <t>Source attribute: tid</t>
   </si>
   <si>
+    <t>Angivelse av tid eller tidsintervall då den provrelaterade aktiviteten utfördes.</t>
+  </si>
+  <si>
     <t>Provrelaterad-aktivitet-Aktivitet.metod</t>
   </si>
   <si>
     <t>Source attribute: metod</t>
+  </si>
+  <si>
+    <t>Kod för metod för provrelaterad aktivitet.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
   </si>
   <si>
     <t>Provrelaterad-aktivitet-Aktivitet.avser</t>
@@ -869,7 +881,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -937,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -963,13 +975,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1020,7 +1032,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1037,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1066,10 +1078,10 @@
         <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1120,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1137,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1163,13 +1175,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1220,7 +1232,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
